--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2050,25 +2050,47 @@
       <c r="N27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="20" t="str">
+      <c r="A28" s="18" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>520</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="I28" s="20" t="n">
         <f aca="false">IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
-        <v/>
-      </c>
-      <c r="J28" s="20" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J28" s="20" t="n">
         <f aca="false">IF(I28="","",1440-I28)</f>
-        <v/>
-      </c>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
+        <v>150</v>
+      </c>
+      <c r="K28" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L28" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M28" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2094,25 +2094,47 @@
       <c r="N28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="20" t="str">
+      <c r="A29" s="18" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I29" s="20" t="n">
         <f aca="false">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
-        <v/>
-      </c>
-      <c r="J29" s="20" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J29" s="20" t="n">
         <f aca="false">IF(I29="","",1440-I29)</f>
-        <v/>
-      </c>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
+        <v>220</v>
+      </c>
+      <c r="K29" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2138,25 +2138,47 @@
       <c r="N29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="20" t="str">
+      <c r="A30" s="18" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>320</v>
+      </c>
+      <c r="I30" s="20" t="n">
         <f aca="false">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
-        <v/>
-      </c>
-      <c r="J30" s="20" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J30" s="20" t="n">
         <f aca="false">IF(I30="","",1440-I30)</f>
-        <v/>
-      </c>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
+        <v>200</v>
+      </c>
+      <c r="K30" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2182,25 +2182,47 @@
       <c r="N30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="20" t="str">
+      <c r="A31" s="18" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I31" s="20" t="n">
         <f aca="false">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="20" t="str">
+        <v>990</v>
+      </c>
+      <c r="J31" s="20" t="n">
         <f aca="false">IF(I31="","",1440-I31)</f>
-        <v/>
-      </c>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
+        <v>450</v>
+      </c>
+      <c r="K31" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2226,25 +2226,47 @@
       <c r="N31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="20" t="str">
+      <c r="A32" s="18" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C32" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="I32" s="20" t="n">
         <f aca="false">IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="20" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J32" s="20" t="n">
         <f aca="false">IF(I32="","",1440-I32)</f>
-        <v/>
-      </c>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
+        <v>290</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2270,25 +2270,47 @@
       <c r="N32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="20" t="str">
+      <c r="A33" s="18" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="I33" s="20" t="n">
         <f aca="false">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="20" t="str">
+        <v>890</v>
+      </c>
+      <c r="J33" s="20" t="n">
         <f aca="false">IF(I33="","",1440-I33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
+        <v>550</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2314,25 +2314,47 @@
       <c r="N33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="20" t="str">
+      <c r="A34" s="18" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>310</v>
+      </c>
+      <c r="I34" s="20" t="n">
         <f aca="false">IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="20" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J34" s="20" t="n">
         <f aca="false">IF(I34="","",1440-I34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21"/>
+        <v>410</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2358,25 +2358,47 @@
       <c r="N34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="20" t="str">
+      <c r="A35" s="18" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I35" s="20" t="n">
         <f aca="false">IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="20" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J35" s="20" t="n">
         <f aca="false">IF(I35="","",1440-I35)</f>
-        <v/>
-      </c>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="21"/>
+        <v>160</v>
+      </c>
+      <c r="K35" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2402,25 +2402,47 @@
       <c r="N35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="20" t="str">
+      <c r="A36" s="18" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>210</v>
+      </c>
+      <c r="I36" s="20" t="n">
         <f aca="false">IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
-        <v/>
-      </c>
-      <c r="J36" s="20" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J36" s="20" t="n">
         <f aca="false">IF(I36="","",1440-I36)</f>
-        <v/>
-      </c>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
+        <v>160</v>
+      </c>
+      <c r="K36" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2446,47 +2446,91 @@
       <c r="N36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="20" t="str">
+      <c r="A37" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>520</v>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="I37" s="20" t="n">
         <f aca="false">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
-        <v/>
-      </c>
-      <c r="J37" s="20" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J37" s="20" t="n">
         <f aca="false">IF(I37="","",1440-I37)</f>
-        <v/>
-      </c>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="21"/>
+        <v>150</v>
+      </c>
+      <c r="K37" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="20" t="str">
+      <c r="A38" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="I38" s="20" t="n">
         <f aca="false">IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
-        <v/>
-      </c>
-      <c r="J38" s="20" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J38" s="20" t="n">
         <f aca="false">IF(I38="","",1440-I38)</f>
-        <v/>
-      </c>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
+        <v>390</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N38" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">Month:</t>
   </si>
   <si>
-    <t xml:space="preserve">August</t>
+    <t xml:space="preserve">September</t>
   </si>
   <si>
     <t xml:space="preserve">All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -2534,47 +2534,91 @@
       <c r="N38" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="20" t="str">
+      <c r="A39" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>110</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="I39" s="20" t="n">
         <f aca="false">IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
-        <v/>
-      </c>
-      <c r="J39" s="20" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J39" s="20" t="n">
         <f aca="false">IF(I39="","",1440-I39)</f>
-        <v/>
-      </c>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
+        <v>280</v>
+      </c>
+      <c r="K39" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="20" t="str">
+      <c r="A40" s="18" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="I40" s="20" t="n">
         <f aca="false">IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
-        <v/>
-      </c>
-      <c r="J40" s="20" t="str">
+        <v>800</v>
+      </c>
+      <c r="J40" s="20" t="n">
         <f aca="false">IF(I40="","",1440-I40)</f>
-        <v/>
-      </c>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
+        <v>640</v>
+      </c>
+      <c r="K40" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2622,25 +2622,47 @@
       <c r="N40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="20" t="str">
+      <c r="A41" s="18" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>550</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I41" s="20" t="n">
         <f aca="false">IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
-        <v/>
-      </c>
-      <c r="J41" s="20" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J41" s="20" t="n">
         <f aca="false">IF(I41="","",1440-I41)</f>
-        <v/>
-      </c>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="21"/>
+        <v>250</v>
+      </c>
+      <c r="K41" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2666,25 +2666,47 @@
       <c r="N41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="20" t="str">
+      <c r="A42" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C42" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="I42" s="20" t="n">
         <f aca="false">IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
-        <v/>
-      </c>
-      <c r="J42" s="20" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J42" s="20" t="n">
         <f aca="false">IF(I42="","",1440-I42)</f>
-        <v/>
-      </c>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="21"/>
+        <v>300</v>
+      </c>
+      <c r="K42" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L42" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M42" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2710,47 +2710,91 @@
       <c r="N42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="20" t="str">
+      <c r="A43" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B43" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C43" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>310</v>
+      </c>
+      <c r="I43" s="20" t="n">
         <f aca="false">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
-        <v/>
-      </c>
-      <c r="J43" s="20" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J43" s="20" t="n">
         <f aca="false">IF(I43="","",1440-I43)</f>
-        <v/>
-      </c>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
+        <v>120</v>
+      </c>
+      <c r="K43" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M43" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="20" t="str">
+      <c r="A44" s="18" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B44" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C44" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G44" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="I44" s="20" t="n">
         <f aca="false">IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
-        <v/>
-      </c>
-      <c r="J44" s="20" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J44" s="20" t="n">
         <f aca="false">IF(I44="","",1440-I44)</f>
-        <v/>
-      </c>
-      <c r="K44" s="21"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="21"/>
+        <v>310</v>
+      </c>
+      <c r="K44" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L44" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M44" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2798,25 +2798,47 @@
       <c r="N44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="20" t="str">
+      <c r="A45" s="18" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B45" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C45" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="20" t="n">
         <f aca="false">IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
-        <v/>
-      </c>
-      <c r="J45" s="20" t="str">
+        <v>770</v>
+      </c>
+      <c r="J45" s="20" t="n">
         <f aca="false">IF(I45="","",1440-I45)</f>
-        <v/>
-      </c>
-      <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
-      <c r="M45" s="21"/>
+        <v>670</v>
+      </c>
+      <c r="K45" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L45" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2842,25 +2842,47 @@
       <c r="N45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="18"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="20" t="str">
+      <c r="A46" s="18" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B46" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>130</v>
+      </c>
+      <c r="I46" s="20" t="n">
         <f aca="false">IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
-        <v/>
-      </c>
-      <c r="J46" s="20" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J46" s="20" t="n">
         <f aca="false">IF(I46="","",1440-I46)</f>
-        <v/>
-      </c>
-      <c r="K46" s="21"/>
-      <c r="L46" s="21"/>
-      <c r="M46" s="21"/>
+        <v>350</v>
+      </c>
+      <c r="K46" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L46" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M46" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2886,25 +2886,47 @@
       <c r="N46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="20" t="str">
+      <c r="A47" s="18" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B47" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C47" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="I47" s="20" t="n">
         <f aca="false">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
-        <v/>
-      </c>
-      <c r="J47" s="20" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J47" s="20" t="n">
         <f aca="false">IF(I47="","",1440-I47)</f>
-        <v/>
-      </c>
-      <c r="K47" s="21"/>
-      <c r="L47" s="21"/>
-      <c r="M47" s="21"/>
+        <v>420</v>
+      </c>
+      <c r="K47" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M47" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2930,25 +2930,47 @@
       <c r="N47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="20" t="str">
+      <c r="A48" s="18" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B48" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C48" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F48" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="I48" s="20" t="n">
         <f aca="false">IF(SUM(B48:F48,H48)=0,"",SUM(B48:F48,H48))</f>
-        <v/>
-      </c>
-      <c r="J48" s="20" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J48" s="20" t="n">
         <f aca="false">IF(I48="","",1440-I48)</f>
-        <v/>
-      </c>
-      <c r="K48" s="21"/>
-      <c r="L48" s="21"/>
-      <c r="M48" s="21"/>
+        <v>370</v>
+      </c>
+      <c r="K48" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M48" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N48" s="22"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2974,47 +2974,91 @@
       <c r="N48" s="22"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="18"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="20" t="str">
+      <c r="A49" s="18" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B49" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C49" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I49" s="20" t="n">
         <f aca="false">IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
-        <v/>
-      </c>
-      <c r="J49" s="20" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J49" s="20" t="n">
         <f aca="false">IF(I49="","",1440-I49)</f>
-        <v/>
-      </c>
-      <c r="K49" s="21"/>
-      <c r="L49" s="21"/>
-      <c r="M49" s="21"/>
+        <v>380</v>
+      </c>
+      <c r="K49" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L49" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M49" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N49" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="20" t="str">
+      <c r="A50" s="18" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B50" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="I50" s="20" t="n">
         <f aca="false">IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
-        <v/>
-      </c>
-      <c r="J50" s="20" t="str">
+        <v>960</v>
+      </c>
+      <c r="J50" s="20" t="n">
         <f aca="false">IF(I50="","",1440-I50)</f>
-        <v/>
-      </c>
-      <c r="K50" s="21"/>
-      <c r="L50" s="21"/>
-      <c r="M50" s="21"/>
+        <v>480</v>
+      </c>
+      <c r="K50" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L50" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M50" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N50" s="22"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3062,25 +3062,47 @@
       <c r="N50" s="22"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="18"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="20" t="str">
+      <c r="A51" s="18" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B51" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>210</v>
+      </c>
+      <c r="I51" s="20" t="n">
         <f aca="false">IF(SUM(B51:F51,H51)=0,"",SUM(B51:F51,H51))</f>
-        <v/>
-      </c>
-      <c r="J51" s="20" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J51" s="20" t="n">
         <f aca="false">IF(I51="","",1440-I51)</f>
-        <v/>
-      </c>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
+        <v>350</v>
+      </c>
+      <c r="K51" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L51" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M51" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N51" s="22"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">Month:</t>
   </si>
   <si>
-    <t xml:space="preserve">September</t>
+    <t xml:space="preserve">October</t>
   </si>
   <si>
     <t xml:space="preserve">All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -3106,25 +3106,47 @@
       <c r="N51" s="22"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="18"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="20" t="str">
+      <c r="A52" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B52" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C52" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I52" s="20" t="n">
         <f aca="false">IF(SUM(B52:F52,H52)=0,"",SUM(B52:F52,H52))</f>
-        <v/>
-      </c>
-      <c r="J52" s="20" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J52" s="20" t="n">
         <f aca="false">IF(I52="","",1440-I52)</f>
-        <v/>
-      </c>
-      <c r="K52" s="21"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
+        <v>350</v>
+      </c>
+      <c r="K52" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M52" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N52" s="22"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3150,25 +3150,47 @@
       <c r="N52" s="22"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="20" t="str">
+      <c r="A53" s="18" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B53" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="I53" s="20" t="n">
         <f aca="false">IF(SUM(B53:F53,H53)=0,"",SUM(B53:F53,H53))</f>
-        <v/>
-      </c>
-      <c r="J53" s="20" t="str">
+        <v>960</v>
+      </c>
+      <c r="J53" s="20" t="n">
         <f aca="false">IF(I53="","",1440-I53)</f>
-        <v/>
-      </c>
-      <c r="K53" s="21"/>
-      <c r="L53" s="21"/>
-      <c r="M53" s="21"/>
+        <v>480</v>
+      </c>
+      <c r="K53" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M53" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N53" s="22"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="n">
-        <v>46267</v>
+        <v>46297</v>
       </c>
       <c r="B53" s="19" t="n">
         <v>600</v>
@@ -3194,25 +3194,47 @@
       <c r="N53" s="22"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="18"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="20" t="str">
+      <c r="A54" s="18" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B54" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C54" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="I54" s="20" t="n">
         <f aca="false">IF(SUM(B54:F54,H54)=0,"",SUM(B54:F54,H54))</f>
-        <v/>
-      </c>
-      <c r="J54" s="20" t="str">
+        <v>930</v>
+      </c>
+      <c r="J54" s="20" t="n">
         <f aca="false">IF(I54="","",1440-I54)</f>
-        <v/>
-      </c>
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="21"/>
+        <v>510</v>
+      </c>
+      <c r="K54" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L54" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M54" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N54" s="22"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3238,25 +3238,47 @@
       <c r="N54" s="22"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="20" t="str">
+      <c r="A55" s="18" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B55" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E55" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="19" t="n">
+        <v>140</v>
+      </c>
+      <c r="I55" s="20" t="n">
         <f aca="false">IF(SUM(B55:F55,H55)=0,"",SUM(B55:F55,H55))</f>
-        <v/>
-      </c>
-      <c r="J55" s="20" t="str">
+        <v>890</v>
+      </c>
+      <c r="J55" s="20" t="n">
         <f aca="false">IF(I55="","",1440-I55)</f>
-        <v/>
-      </c>
-      <c r="K55" s="21"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="21"/>
+        <v>550</v>
+      </c>
+      <c r="K55" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L55" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M55" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N55" s="22"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3282,47 +3282,91 @@
       <c r="N55" s="22"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="18"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="20" t="str">
+      <c r="A56" s="18" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B56" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F56" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G56" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="I56" s="20" t="n">
         <f aca="false">IF(SUM(B56:F56,H56)=0,"",SUM(B56:F56,H56))</f>
-        <v/>
-      </c>
-      <c r="J56" s="20" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J56" s="20" t="n">
         <f aca="false">IF(I56="","",1440-I56)</f>
-        <v/>
-      </c>
-      <c r="K56" s="21"/>
-      <c r="L56" s="21"/>
-      <c r="M56" s="21"/>
+        <v>300</v>
+      </c>
+      <c r="K56" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L56" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M56" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N56" s="22"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="18"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="20" t="str">
+      <c r="A57" s="18" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B57" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G57" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I57" s="20" t="n">
         <f aca="false">IF(SUM(B57:F57,H57)=0,"",SUM(B57:F57,H57))</f>
-        <v/>
-      </c>
-      <c r="J57" s="20" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J57" s="20" t="n">
         <f aca="false">IF(I57="","",1440-I57)</f>
-        <v/>
-      </c>
-      <c r="K57" s="21"/>
-      <c r="L57" s="21"/>
-      <c r="M57" s="21"/>
+        <v>400</v>
+      </c>
+      <c r="K57" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L57" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M57" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N57" s="22"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3370,25 +3370,47 @@
       <c r="N57" s="22"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="18"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="20" t="str">
+      <c r="A58" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G58" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I58" s="20" t="n">
         <f aca="false">IF(SUM(B58:F58,H58)=0,"",SUM(B58:F58,H58))</f>
-        <v/>
-      </c>
-      <c r="J58" s="20" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J58" s="20" t="n">
         <f aca="false">IF(I58="","",1440-I58)</f>
-        <v/>
-      </c>
-      <c r="K58" s="21"/>
-      <c r="L58" s="21"/>
-      <c r="M58" s="21"/>
+        <v>340</v>
+      </c>
+      <c r="K58" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L58" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M58" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="N58" s="22"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8529A9-3CD7-4739-89BE-09B970A0BDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D833E15A-64D8-4FAE-8471-528B9E3E452D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3465,47 +3465,91 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B62" s="14">
+        <v>500</v>
+      </c>
+      <c r="C62" s="14">
+        <v>30</v>
+      </c>
+      <c r="D62" s="14">
+        <v>200</v>
+      </c>
+      <c r="E62" s="14">
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>100</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B63" s="14">
+        <v>500</v>
+      </c>
+      <c r="C63" s="14">
+        <v>30</v>
+      </c>
+      <c r="D63" s="14">
+        <v>200</v>
+      </c>
+      <c r="E63" s="14">
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>150</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
+        <v>560</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D833E15A-64D8-4FAE-8471-528B9E3E452D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2E3A13-3453-4AAA-89E1-8B780A4B7CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="13">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B63" s="14">
         <v>500</v>
@@ -3553,25 +3553,47 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B64" s="14">
+        <v>450</v>
+      </c>
+      <c r="C64" s="14">
+        <v>30</v>
+      </c>
+      <c r="D64" s="14">
+        <v>200</v>
+      </c>
+      <c r="E64" s="14">
+        <v>0</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>100</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -3583,14 +3605,8 @@
       <c r="F65" s="14"/>
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
       <c r="K65" s="16"/>
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2E3A13-3453-4AAA-89E1-8B780A4B7CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EB909E-1091-4D7B-8B75-63883929D7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3597,63 +3597,135 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
+      <c r="A65" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B65" s="14">
+        <v>450</v>
+      </c>
+      <c r="C65" s="14">
+        <v>30</v>
+      </c>
+      <c r="D65" s="14">
+        <v>200</v>
+      </c>
+      <c r="E65" s="14">
+        <v>0</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>120</v>
+      </c>
+      <c r="I65" s="15">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J65" s="15">
+        <f t="shared" si="1"/>
+        <v>640</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B66" s="14">
+        <v>450</v>
+      </c>
+      <c r="C66" s="14">
+        <v>30</v>
+      </c>
+      <c r="D66" s="14">
+        <v>200</v>
+      </c>
+      <c r="E66" s="14">
+        <v>0</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>100</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B67" s="14">
+        <v>450</v>
+      </c>
+      <c r="C67" s="14">
+        <v>30</v>
+      </c>
+      <c r="D67" s="14">
+        <v>200</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>90</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
+        <v>670</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EB909E-1091-4D7B-8B75-63883929D7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF47FF2-97A6-4580-A06D-B05681B7D3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3729,25 +3729,47 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B68" s="14">
+        <v>500</v>
+      </c>
+      <c r="C68" s="14">
+        <v>30</v>
+      </c>
+      <c r="D68" s="14">
+        <v>0</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>300</v>
+      </c>
+      <c r="H68" s="14">
+        <v>0</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
+        <v>910</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF47FF2-97A6-4580-A06D-B05681B7D3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1D6908-3B7F-4960-B739-995A288897A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3748,18 +3748,18 @@
         <v>0</v>
       </c>
       <c r="G68" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H68" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v>530</v>
+        <v>730</v>
       </c>
       <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v>910</v>
+        <v>710</v>
       </c>
       <c r="K68" s="16" t="s">
         <v>53</v>
@@ -3773,25 +3773,47 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B69" s="14">
+        <v>500</v>
+      </c>
+      <c r="C69" s="14">
+        <v>30</v>
+      </c>
+      <c r="D69" s="14">
+        <v>0</v>
+      </c>
+      <c r="E69" s="14">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>300</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1D6908-3B7F-4960-B739-995A288897A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941EA9FD-6A91-4347-BFDE-B1BF2FA487C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3817,25 +3817,47 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B70" s="14">
+        <v>500</v>
+      </c>
+      <c r="C70" s="14">
+        <v>30</v>
+      </c>
+      <c r="D70" s="14">
+        <v>60</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>1</v>
+      </c>
+      <c r="G70" s="14">
+        <v>50</v>
+      </c>
+      <c r="H70" s="14">
+        <v>100</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>691</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
+        <v>749</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941EA9FD-6A91-4347-BFDE-B1BF2FA487C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B05BA30-2351-4094-8550-727601071E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3861,25 +3861,47 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B71" s="14">
+        <v>500</v>
+      </c>
+      <c r="C71" s="14">
+        <v>30</v>
+      </c>
+      <c r="D71" s="14">
+        <v>0</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>300</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B05BA30-2351-4094-8550-727601071E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2F5702-9A63-4D9D-A1B0-681025940A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3905,25 +3905,47 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B72" s="14">
+        <v>500</v>
+      </c>
+      <c r="C72" s="14">
+        <v>30</v>
+      </c>
+      <c r="D72" s="14">
+        <v>120</v>
+      </c>
+      <c r="E72" s="14">
+        <v>30</v>
+      </c>
+      <c r="F72" s="14">
+        <v>5</v>
+      </c>
+      <c r="G72" s="14">
+        <v>250</v>
+      </c>
+      <c r="H72" s="14">
+        <v>120</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>805</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
+        <v>635</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2F5702-9A63-4D9D-A1B0-681025940A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2211E114-D71A-4CD7-B6D5-63D84323E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3949,25 +3949,47 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B73" s="14">
+        <v>500</v>
+      </c>
+      <c r="C73" s="14">
+        <v>30</v>
+      </c>
+      <c r="D73" s="14">
+        <v>100</v>
+      </c>
+      <c r="E73" s="14">
+        <v>50</v>
+      </c>
+      <c r="F73" s="14">
+        <v>6</v>
+      </c>
+      <c r="G73" s="14">
+        <v>300</v>
+      </c>
+      <c r="H73" s="14">
+        <v>100</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>786</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+        <v>654</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2211E114-D71A-4CD7-B6D5-63D84323E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043F7B29-7A33-4151-BDE9-AE67E3F76971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3993,47 +3993,91 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B74" s="14">
+        <v>500</v>
+      </c>
+      <c r="C74" s="14">
+        <v>30</v>
+      </c>
+      <c r="D74" s="14">
+        <v>100</v>
+      </c>
+      <c r="E74" s="14">
+        <v>0</v>
+      </c>
+      <c r="F74" s="14">
+        <v>4</v>
+      </c>
+      <c r="G74" s="14">
+        <v>200</v>
+      </c>
+      <c r="H74" s="14">
+        <v>120</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>754</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
+        <v>686</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B75" s="14">
+        <v>500</v>
+      </c>
+      <c r="C75" s="14">
+        <v>30</v>
+      </c>
+      <c r="D75" s="14">
+        <v>60</v>
+      </c>
+      <c r="E75" s="14">
+        <v>100</v>
+      </c>
+      <c r="F75" s="14">
+        <v>2</v>
+      </c>
+      <c r="G75" s="14">
+        <v>100</v>
+      </c>
+      <c r="H75" s="14">
+        <v>300</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>992</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
+        <v>448</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043F7B29-7A33-4151-BDE9-AE67E3F76971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A98D49-23E6-4E20-88D5-EA628C1C3E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4081,25 +4081,47 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B76" s="14">
+        <v>500</v>
+      </c>
+      <c r="C76" s="14">
+        <v>30</v>
+      </c>
+      <c r="D76" s="14">
+        <v>60</v>
+      </c>
+      <c r="E76" s="14">
+        <v>0</v>
+      </c>
+      <c r="F76" s="14">
+        <v>0</v>
+      </c>
+      <c r="G76" s="14">
+        <v>0</v>
+      </c>
+      <c r="H76" s="14">
+        <v>100</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
+        <v>750</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A98D49-23E6-4E20-88D5-EA628C1C3E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9C91AF-F30B-414F-8902-CB21A46D55E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4125,25 +4125,47 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B77" s="14">
+        <v>500</v>
+      </c>
+      <c r="C77" s="14">
+        <v>30</v>
+      </c>
+      <c r="D77" s="14">
+        <v>60</v>
+      </c>
+      <c r="E77" s="14">
+        <v>30</v>
+      </c>
+      <c r="F77" s="14">
+        <v>0</v>
+      </c>
+      <c r="G77" s="14">
+        <v>0</v>
+      </c>
+      <c r="H77" s="14">
+        <v>120</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
+        <v>700</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9C91AF-F30B-414F-8902-CB21A46D55E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82F30BB-6AE1-46FC-97AA-44B11D754211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3833,21 +3833,21 @@
         <v>0</v>
       </c>
       <c r="F70" s="14">
+        <v>50</v>
+      </c>
+      <c r="G70" s="14">
         <v>1</v>
-      </c>
-      <c r="G70" s="14">
-        <v>50</v>
       </c>
       <c r="H70" s="14">
         <v>100</v>
       </c>
       <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v>691</v>
+        <v>740</v>
       </c>
       <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v>749</v>
+        <v>700</v>
       </c>
       <c r="K70" s="16" t="s">
         <v>53</v>
@@ -3921,21 +3921,21 @@
         <v>30</v>
       </c>
       <c r="F72" s="14">
+        <v>250</v>
+      </c>
+      <c r="G72" s="14">
         <v>5</v>
-      </c>
-      <c r="G72" s="14">
-        <v>250</v>
       </c>
       <c r="H72" s="14">
         <v>120</v>
       </c>
       <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v>805</v>
+        <v>1050</v>
       </c>
       <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v>635</v>
+        <v>390</v>
       </c>
       <c r="K72" s="16" t="s">
         <v>53</v>
@@ -3965,21 +3965,21 @@
         <v>50</v>
       </c>
       <c r="F73" s="14">
+        <v>300</v>
+      </c>
+      <c r="G73" s="14">
         <v>6</v>
-      </c>
-      <c r="G73" s="14">
-        <v>300</v>
       </c>
       <c r="H73" s="14">
         <v>100</v>
       </c>
       <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v>786</v>
+        <v>1080</v>
       </c>
       <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v>654</v>
+        <v>360</v>
       </c>
       <c r="K73" s="16" t="s">
         <v>53</v>
@@ -4009,21 +4009,21 @@
         <v>0</v>
       </c>
       <c r="F74" s="14">
+        <v>200</v>
+      </c>
+      <c r="G74" s="14">
         <v>4</v>
-      </c>
-      <c r="G74" s="14">
-        <v>200</v>
       </c>
       <c r="H74" s="14">
         <v>120</v>
       </c>
       <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v>754</v>
+        <v>950</v>
       </c>
       <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v>686</v>
+        <v>490</v>
       </c>
       <c r="K74" s="16" t="s">
         <v>53</v>
@@ -4053,21 +4053,21 @@
         <v>100</v>
       </c>
       <c r="F75" s="14">
+        <v>100</v>
+      </c>
+      <c r="G75" s="14">
         <v>2</v>
-      </c>
-      <c r="G75" s="14">
-        <v>100</v>
       </c>
       <c r="H75" s="14">
         <v>300</v>
       </c>
       <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v>992</v>
+        <v>1090</v>
       </c>
       <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v>448</v>
+        <v>350</v>
       </c>
       <c r="K75" s="16" t="s">
         <v>53</v>
@@ -4169,47 +4169,91 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B78" s="14">
+        <v>500</v>
+      </c>
+      <c r="C78" s="14">
+        <v>30</v>
+      </c>
+      <c r="D78" s="14">
+        <v>60</v>
+      </c>
+      <c r="E78" s="14">
+        <v>30</v>
+      </c>
+      <c r="F78" s="14">
+        <v>300</v>
+      </c>
+      <c r="G78" s="14">
+        <v>6</v>
+      </c>
+      <c r="H78" s="14">
+        <v>100</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B79" s="14">
+        <v>500</v>
+      </c>
+      <c r="C79" s="14">
+        <v>30</v>
+      </c>
+      <c r="D79" s="14">
+        <v>30</v>
+      </c>
+      <c r="E79" s="14">
+        <v>10</v>
+      </c>
+      <c r="F79" s="14">
+        <v>300</v>
+      </c>
+      <c r="G79" s="14">
+        <v>6</v>
+      </c>
+      <c r="H79" s="14">
+        <v>60</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">

--- a/12629017.xlsx
+++ b/12629017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82F30BB-6AE1-46FC-97AA-44B11D754211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5B2198-B39C-4491-B8C7-8BC6D3C95B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4257,47 +4257,91 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+      <c r="A80" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B80" s="14">
+        <v>500</v>
+      </c>
+      <c r="C80" s="14">
+        <v>30</v>
+      </c>
+      <c r="D80" s="14">
+        <v>30</v>
+      </c>
+      <c r="E80" s="14">
+        <v>10</v>
+      </c>
+      <c r="F80" s="14">
+        <v>100</v>
+      </c>
+      <c r="G80" s="14">
+        <v>2</v>
+      </c>
+      <c r="H80" s="14">
+        <v>100</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
+        <v>670</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+      <c r="A81" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B81" s="14">
+        <v>500</v>
+      </c>
+      <c r="C81" s="14">
+        <v>30</v>
+      </c>
+      <c r="D81" s="14">
+        <v>30</v>
+      </c>
+      <c r="E81" s="14">
+        <v>20</v>
+      </c>
+      <c r="F81" s="14">
+        <v>300</v>
+      </c>
+      <c r="G81" s="14">
+        <v>6</v>
+      </c>
+      <c r="H81" s="14">
+        <v>100</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N81" s="17"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
